--- a/origin_obstacle_states_mid.xlsx
+++ b/origin_obstacle_states_mid.xlsx
@@ -421,7 +421,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C1" t="n">
         <v>4</v>
@@ -451,7 +451,7 @@
         <v>6</v>
       </c>
       <c r="L1" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M1" t="n">
         <v>14</v>
@@ -460,7 +460,7 @@
         <v>15</v>
       </c>
       <c r="O1" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="P1" t="n">
         <v>5</v>
@@ -471,13 +471,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -501,7 +501,7 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -510,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>11</v>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>7</v>
@@ -536,7 +536,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
